--- a/environment/seed/sources/Shared/Finance/FP&A/FY27 plan/FY27 planning assumptions - v6 controller tie.xlsx
+++ b/environment/seed/sources/Shared/Finance/FP&A/FY27 plan/FY27 planning assumptions - v6 controller tie.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="R525ce503da634e01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue and Service" sheetId="2" r:id="Rca73355794524f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin and Accuracy" sheetId="3" r:id="R7f36e6f7b48c4e21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opex and Workforce" sheetId="4" r:id="R883794bd0ced4ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branches and Backlog" sheetId="5" r:id="Rc45cb80477aa4f9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working Capital" sheetId="6" r:id="Rd81eb7a67d6a4586"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Checks" sheetId="7" r:id="R8bfeb901081941fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" r:id="rId5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue and Service" sheetId="2" r:id="rId6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin and Accuracy" sheetId="3" r:id="rId7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opex and Workforce" sheetId="4" r:id="rId8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Branches and Backlog" sheetId="5" r:id="rId9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working Capital" sheetId="6" r:id="rId10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Checks" sheetId="7" r:id="rId11"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -266,7 +266,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{F7EA7B2A-C9E1-4FC9-9E15-130629A231F7}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{BD67AABD-AFE6-B47E-2605-AD863483D933}"/>
 </xltc:personList>
 </file>
 
@@ -37119,7 +37119,7 @@
         <x:v>PLN-00674</x:v>
       </x:c>
       <x:c r="B38" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C38" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37137,14 +37137,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="H38" s="31" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I38" s="28" t="str"/>
       <x:c r="J38" s="28" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="K38" s="28" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L38" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37156,7 +37156,7 @@
         <x:v>PLN-00675</x:v>
       </x:c>
       <x:c r="B39" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C39" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37181,7 +37181,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K39" s="28" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L39" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37193,7 +37193,7 @@
         <x:v>PLN-00676</x:v>
       </x:c>
       <x:c r="B40" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C40" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37218,7 +37218,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K40" s="28" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L40" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37230,7 +37230,7 @@
         <x:v>PLN-00693</x:v>
       </x:c>
       <x:c r="B41" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C41" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37248,14 +37248,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="H41" s="31" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I41" s="28" t="str"/>
       <x:c r="J41" s="28" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="K41" s="28" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L41" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37267,7 +37267,7 @@
         <x:v>PLN-00694</x:v>
       </x:c>
       <x:c r="B42" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C42" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37292,7 +37292,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K42" s="28" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L42" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37304,7 +37304,7 @@
         <x:v>PLN-00695</x:v>
       </x:c>
       <x:c r="B43" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C43" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37329,7 +37329,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K43" s="28" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L43" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37341,7 +37341,7 @@
         <x:v>PLN-00711</x:v>
       </x:c>
       <x:c r="B44" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C44" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37366,7 +37366,7 @@
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="K44" s="28" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L44" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37378,7 +37378,7 @@
         <x:v>PLN-00712</x:v>
       </x:c>
       <x:c r="B45" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C45" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37403,7 +37403,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K45" s="28" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L45" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37415,7 +37415,7 @@
         <x:v>PLN-00713</x:v>
       </x:c>
       <x:c r="B46" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C46" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37440,7 +37440,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K46" s="28" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L46" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37452,7 +37452,7 @@
         <x:v>PLN-00727</x:v>
       </x:c>
       <x:c r="B47" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C47" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37470,14 +37470,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="H47" s="31" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I47" s="28" t="str"/>
       <x:c r="J47" s="28" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="K47" s="28" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L47" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37489,7 +37489,7 @@
         <x:v>PLN-00728</x:v>
       </x:c>
       <x:c r="B48" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C48" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37514,7 +37514,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K48" s="28" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L48" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37526,7 +37526,7 @@
         <x:v>PLN-00729</x:v>
       </x:c>
       <x:c r="B49" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C49" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37551,7 +37551,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K49" s="28" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L49" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37563,7 +37563,7 @@
         <x:v>PLN-00741</x:v>
       </x:c>
       <x:c r="B50" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C50" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37581,14 +37581,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="H50" s="31" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I50" s="28" t="str"/>
       <x:c r="J50" s="28" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="K50" s="28" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L50" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37600,7 +37600,7 @@
         <x:v>PLN-00742</x:v>
       </x:c>
       <x:c r="B51" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C51" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37625,7 +37625,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K51" s="28" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L51" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37637,7 +37637,7 @@
         <x:v>PLN-00743</x:v>
       </x:c>
       <x:c r="B52" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C52" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37662,7 +37662,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K52" s="28" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L52" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37674,7 +37674,7 @@
         <x:v>PLN-00754</x:v>
       </x:c>
       <x:c r="B53" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C53" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37692,14 +37692,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="H53" s="31" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I53" s="28" t="str"/>
       <x:c r="J53" s="28" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="K53" s="28" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L53" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37711,7 +37711,7 @@
         <x:v>PLN-00755</x:v>
       </x:c>
       <x:c r="B54" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C54" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37736,7 +37736,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K54" s="28" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L54" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37748,7 +37748,7 @@
         <x:v>PLN-00756</x:v>
       </x:c>
       <x:c r="B55" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C55" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37773,7 +37773,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K55" s="28" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L55" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37785,7 +37785,7 @@
         <x:v>PLN-00766</x:v>
       </x:c>
       <x:c r="B56" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C56" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37803,14 +37803,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="H56" s="31" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I56" s="28" t="str"/>
       <x:c r="J56" s="28" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="K56" s="28" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L56" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37822,7 +37822,7 @@
         <x:v>PLN-00767</x:v>
       </x:c>
       <x:c r="B57" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C57" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37847,7 +37847,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K57" s="28" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L57" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37859,7 +37859,7 @@
         <x:v>PLN-00768</x:v>
       </x:c>
       <x:c r="B58" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C58" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37884,7 +37884,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K58" s="28" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L58" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37896,7 +37896,7 @@
         <x:v>PLN-00777</x:v>
       </x:c>
       <x:c r="B59" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C59" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37914,14 +37914,14 @@
         <x:v>Customer delivery priority</x:v>
       </x:c>
       <x:c r="H59" s="31" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I59" s="28" t="str"/>
       <x:c r="J59" s="28" t="str">
         <x:v>priority rank</x:v>
       </x:c>
       <x:c r="K59" s="28" t="str">
-        <x:v>Approved project-execution register</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L59" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37933,7 +37933,7 @@
         <x:v>PLN-00778</x:v>
       </x:c>
       <x:c r="B60" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C60" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37958,7 +37958,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K60" s="28" t="str">
-        <x:v>Controller-approved project economics</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L60" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -37970,7 +37970,7 @@
         <x:v>PLN-00779</x:v>
       </x:c>
       <x:c r="B61" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C61" s="28" t="str">
         <x:v>Execution authority</x:v>
@@ -37995,7 +37995,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K61" s="28" t="str">
-        <x:v>Executed contract terms</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L61" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38007,7 +38007,7 @@
         <x:v>PLN-00783</x:v>
       </x:c>
       <x:c r="B62" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C62" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38032,7 +38032,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K62" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L62" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38044,7 +38044,7 @@
         <x:v>PLN-00784</x:v>
       </x:c>
       <x:c r="B63" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C63" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38069,7 +38069,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K63" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L63" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38081,7 +38081,7 @@
         <x:v>PLN-00785</x:v>
       </x:c>
       <x:c r="B64" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C64" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38106,7 +38106,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K64" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L64" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38118,7 +38118,7 @@
         <x:v>PLN-00786</x:v>
       </x:c>
       <x:c r="B65" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C65" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38143,7 +38143,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K65" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L65" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38155,7 +38155,7 @@
         <x:v>PLN-00787</x:v>
       </x:c>
       <x:c r="B66" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C66" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38180,7 +38180,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K66" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L66" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38192,7 +38192,7 @@
         <x:v>PLN-00788</x:v>
       </x:c>
       <x:c r="B67" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C67" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38217,7 +38217,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K67" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L67" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38229,7 +38229,7 @@
         <x:v>PLN-00789</x:v>
       </x:c>
       <x:c r="B68" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C68" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38254,7 +38254,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K68" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L68" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38266,7 +38266,7 @@
         <x:v>PLN-00790</x:v>
       </x:c>
       <x:c r="B69" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C69" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38291,7 +38291,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K69" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L69" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38303,7 +38303,7 @@
         <x:v>PLN-00791</x:v>
       </x:c>
       <x:c r="B70" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C70" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38328,7 +38328,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K70" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L70" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38340,7 +38340,7 @@
         <x:v>PLN-00792</x:v>
       </x:c>
       <x:c r="B71" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C71" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38365,7 +38365,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K71" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L71" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38377,7 +38377,7 @@
         <x:v>PLN-00793</x:v>
       </x:c>
       <x:c r="B72" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C72" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38402,7 +38402,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K72" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L72" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38414,7 +38414,7 @@
         <x:v>PLN-00794</x:v>
       </x:c>
       <x:c r="B73" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C73" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38439,7 +38439,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K73" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L73" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38451,7 +38451,7 @@
         <x:v>PLN-00795</x:v>
       </x:c>
       <x:c r="B74" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C74" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38476,7 +38476,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K74" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L74" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38488,7 +38488,7 @@
         <x:v>PLN-00796</x:v>
       </x:c>
       <x:c r="B75" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C75" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38513,7 +38513,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K75" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L75" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38525,7 +38525,7 @@
         <x:v>PLN-00797</x:v>
       </x:c>
       <x:c r="B76" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C76" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38550,7 +38550,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K76" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L76" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38562,7 +38562,7 @@
         <x:v>PLN-00798</x:v>
       </x:c>
       <x:c r="B77" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C77" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38587,7 +38587,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K77" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L77" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38599,7 +38599,7 @@
         <x:v>PLN-00799</x:v>
       </x:c>
       <x:c r="B78" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C78" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38624,7 +38624,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K78" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L78" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38636,7 +38636,7 @@
         <x:v>PLN-00800</x:v>
       </x:c>
       <x:c r="B79" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C79" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38661,7 +38661,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K79" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L79" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38673,7 +38673,7 @@
         <x:v>PLN-00801</x:v>
       </x:c>
       <x:c r="B80" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C80" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38698,7 +38698,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K80" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L80" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38710,7 +38710,7 @@
         <x:v>PLN-00802</x:v>
       </x:c>
       <x:c r="B81" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C81" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38735,7 +38735,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K81" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L81" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38747,7 +38747,7 @@
         <x:v>PLN-00803</x:v>
       </x:c>
       <x:c r="B82" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C82" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38772,7 +38772,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K82" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L82" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38784,7 +38784,7 @@
         <x:v>PLN-00804</x:v>
       </x:c>
       <x:c r="B83" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C83" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38809,7 +38809,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K83" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L83" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38821,7 +38821,7 @@
         <x:v>PLN-00805</x:v>
       </x:c>
       <x:c r="B84" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C84" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38846,7 +38846,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K84" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L84" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38858,7 +38858,7 @@
         <x:v>PLN-00806</x:v>
       </x:c>
       <x:c r="B85" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C85" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -38883,7 +38883,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K85" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L85" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38895,7 +38895,7 @@
         <x:v>PLN-00807</x:v>
       </x:c>
       <x:c r="B86" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C86" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38920,7 +38920,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K86" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L86" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38932,7 +38932,7 @@
         <x:v>PLN-00808</x:v>
       </x:c>
       <x:c r="B87" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C87" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38957,7 +38957,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K87" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L87" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -38969,7 +38969,7 @@
         <x:v>PLN-00809</x:v>
       </x:c>
       <x:c r="B88" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C88" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -38994,7 +38994,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K88" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L88" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39006,7 +39006,7 @@
         <x:v>PLN-00810</x:v>
       </x:c>
       <x:c r="B89" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C89" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39031,7 +39031,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K89" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L89" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39043,7 +39043,7 @@
         <x:v>PLN-00811</x:v>
       </x:c>
       <x:c r="B90" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C90" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39068,7 +39068,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K90" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L90" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39080,7 +39080,7 @@
         <x:v>PLN-00812</x:v>
       </x:c>
       <x:c r="B91" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C91" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39105,7 +39105,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K91" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L91" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39117,7 +39117,7 @@
         <x:v>PLN-00813</x:v>
       </x:c>
       <x:c r="B92" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C92" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39142,7 +39142,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K92" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L92" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39154,7 +39154,7 @@
         <x:v>PLN-00814</x:v>
       </x:c>
       <x:c r="B93" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C93" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39179,7 +39179,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K93" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L93" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39191,7 +39191,7 @@
         <x:v>PLN-00815</x:v>
       </x:c>
       <x:c r="B94" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C94" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39216,7 +39216,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K94" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L94" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39228,7 +39228,7 @@
         <x:v>PLN-00816</x:v>
       </x:c>
       <x:c r="B95" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C95" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39253,7 +39253,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K95" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L95" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39265,7 +39265,7 @@
         <x:v>PLN-00817</x:v>
       </x:c>
       <x:c r="B96" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C96" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39290,7 +39290,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K96" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L96" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39302,7 +39302,7 @@
         <x:v>PLN-00818</x:v>
       </x:c>
       <x:c r="B97" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C97" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39327,7 +39327,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K97" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L97" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39339,7 +39339,7 @@
         <x:v>PLN-00819</x:v>
       </x:c>
       <x:c r="B98" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C98" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39364,7 +39364,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K98" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L98" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39376,7 +39376,7 @@
         <x:v>PLN-00820</x:v>
       </x:c>
       <x:c r="B99" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C99" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39401,7 +39401,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K99" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L99" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39413,7 +39413,7 @@
         <x:v>PLN-00821</x:v>
       </x:c>
       <x:c r="B100" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C100" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39438,7 +39438,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K100" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L100" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39450,7 +39450,7 @@
         <x:v>PLN-00822</x:v>
       </x:c>
       <x:c r="B101" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C101" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39475,7 +39475,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K101" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L101" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39487,7 +39487,7 @@
         <x:v>PLN-00823</x:v>
       </x:c>
       <x:c r="B102" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C102" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39512,7 +39512,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K102" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L102" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39524,7 +39524,7 @@
         <x:v>PLN-00824</x:v>
       </x:c>
       <x:c r="B103" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C103" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39549,7 +39549,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K103" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L103" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39561,7 +39561,7 @@
         <x:v>PLN-00825</x:v>
       </x:c>
       <x:c r="B104" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C104" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39586,7 +39586,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K104" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L104" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39598,7 +39598,7 @@
         <x:v>PLN-00826</x:v>
       </x:c>
       <x:c r="B105" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C105" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39623,7 +39623,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K105" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L105" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39635,7 +39635,7 @@
         <x:v>PLN-00827</x:v>
       </x:c>
       <x:c r="B106" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C106" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39660,7 +39660,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K106" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L106" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39672,7 +39672,7 @@
         <x:v>PLN-00828</x:v>
       </x:c>
       <x:c r="B107" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C107" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39697,7 +39697,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K107" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L107" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39709,7 +39709,7 @@
         <x:v>PLN-00829</x:v>
       </x:c>
       <x:c r="B108" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C108" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39734,7 +39734,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K108" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L108" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39746,7 +39746,7 @@
         <x:v>PLN-00830</x:v>
       </x:c>
       <x:c r="B109" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C109" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39771,7 +39771,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K109" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L109" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39783,7 +39783,7 @@
         <x:v>PLN-00831</x:v>
       </x:c>
       <x:c r="B110" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C110" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39808,7 +39808,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K110" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L110" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39820,7 +39820,7 @@
         <x:v>PLN-00832</x:v>
       </x:c>
       <x:c r="B111" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C111" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39845,7 +39845,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K111" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L111" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39857,7 +39857,7 @@
         <x:v>PLN-00833</x:v>
       </x:c>
       <x:c r="B112" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C112" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39882,7 +39882,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K112" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L112" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39894,7 +39894,7 @@
         <x:v>PLN-00834</x:v>
       </x:c>
       <x:c r="B113" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C113" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -39919,7 +39919,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K113" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L113" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39931,7 +39931,7 @@
         <x:v>PLN-00835</x:v>
       </x:c>
       <x:c r="B114" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C114" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39956,7 +39956,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K114" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L114" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -39968,7 +39968,7 @@
         <x:v>PLN-00836</x:v>
       </x:c>
       <x:c r="B115" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C115" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -39993,7 +39993,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K115" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L115" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40005,7 +40005,7 @@
         <x:v>PLN-00837</x:v>
       </x:c>
       <x:c r="B116" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C116" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40030,7 +40030,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K116" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L116" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40042,7 +40042,7 @@
         <x:v>PLN-00838</x:v>
       </x:c>
       <x:c r="B117" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C117" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40067,7 +40067,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K117" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L117" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40079,7 +40079,7 @@
         <x:v>PLN-00839</x:v>
       </x:c>
       <x:c r="B118" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C118" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40104,7 +40104,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K118" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L118" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40116,7 +40116,7 @@
         <x:v>PLN-00840</x:v>
       </x:c>
       <x:c r="B119" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C119" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40141,7 +40141,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K119" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L119" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40153,7 +40153,7 @@
         <x:v>PLN-00841</x:v>
       </x:c>
       <x:c r="B120" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C120" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40178,7 +40178,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K120" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L120" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40190,7 +40190,7 @@
         <x:v>PLN-00842</x:v>
       </x:c>
       <x:c r="B121" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C121" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40215,7 +40215,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K121" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L121" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40227,7 +40227,7 @@
         <x:v>PLN-00843</x:v>
       </x:c>
       <x:c r="B122" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C122" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40252,7 +40252,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K122" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L122" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40264,7 +40264,7 @@
         <x:v>PLN-00844</x:v>
       </x:c>
       <x:c r="B123" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C123" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40289,7 +40289,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K123" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L123" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40301,7 +40301,7 @@
         <x:v>PLN-00845</x:v>
       </x:c>
       <x:c r="B124" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C124" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40326,7 +40326,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K124" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L124" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40338,7 +40338,7 @@
         <x:v>PLN-00846</x:v>
       </x:c>
       <x:c r="B125" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C125" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40363,7 +40363,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K125" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L125" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40375,7 +40375,7 @@
         <x:v>PLN-00847</x:v>
       </x:c>
       <x:c r="B126" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C126" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40400,7 +40400,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K126" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L126" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40412,7 +40412,7 @@
         <x:v>PLN-00848</x:v>
       </x:c>
       <x:c r="B127" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C127" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40437,7 +40437,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K127" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L127" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40449,7 +40449,7 @@
         <x:v>PLN-00849</x:v>
       </x:c>
       <x:c r="B128" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C128" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40474,7 +40474,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K128" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L128" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40486,7 +40486,7 @@
         <x:v>PLN-00850</x:v>
       </x:c>
       <x:c r="B129" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C129" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40511,7 +40511,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K129" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L129" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40523,7 +40523,7 @@
         <x:v>PLN-00851</x:v>
       </x:c>
       <x:c r="B130" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C130" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40548,7 +40548,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K130" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L130" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40560,7 +40560,7 @@
         <x:v>PLN-00852</x:v>
       </x:c>
       <x:c r="B131" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C131" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40585,7 +40585,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K131" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L131" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40597,7 +40597,7 @@
         <x:v>PLN-00853</x:v>
       </x:c>
       <x:c r="B132" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C132" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40622,7 +40622,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K132" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L132" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40634,7 +40634,7 @@
         <x:v>PLN-00854</x:v>
       </x:c>
       <x:c r="B133" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C133" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40659,7 +40659,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K133" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L133" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40671,7 +40671,7 @@
         <x:v>PLN-00855</x:v>
       </x:c>
       <x:c r="B134" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C134" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40696,7 +40696,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K134" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L134" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40708,7 +40708,7 @@
         <x:v>PLN-00856</x:v>
       </x:c>
       <x:c r="B135" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C135" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40733,7 +40733,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K135" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L135" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40745,7 +40745,7 @@
         <x:v>PLN-00857</x:v>
       </x:c>
       <x:c r="B136" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C136" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40770,7 +40770,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K136" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L136" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40782,7 +40782,7 @@
         <x:v>PLN-00858</x:v>
       </x:c>
       <x:c r="B137" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C137" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40807,7 +40807,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K137" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L137" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40819,7 +40819,7 @@
         <x:v>PLN-00859</x:v>
       </x:c>
       <x:c r="B138" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C138" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40844,7 +40844,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K138" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L138" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40856,7 +40856,7 @@
         <x:v>PLN-00860</x:v>
       </x:c>
       <x:c r="B139" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C139" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40881,7 +40881,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K139" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L139" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40893,7 +40893,7 @@
         <x:v>PLN-00861</x:v>
       </x:c>
       <x:c r="B140" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C140" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40918,7 +40918,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K140" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L140" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40930,7 +40930,7 @@
         <x:v>PLN-00862</x:v>
       </x:c>
       <x:c r="B141" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C141" s="28" t="str">
         <x:v>Monthly capacity</x:v>
@@ -40955,7 +40955,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K141" s="28" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L141" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -40967,7 +40967,7 @@
         <x:v>PLN-00863</x:v>
       </x:c>
       <x:c r="B142" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C142" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -40992,7 +40992,7 @@
         <x:v>decimal ratio</x:v>
       </x:c>
       <x:c r="K142" s="28" t="str">
-        <x:v>Approved capacity-response policy</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L142" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -41004,7 +41004,7 @@
         <x:v>PLN-00864</x:v>
       </x:c>
       <x:c r="B143" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C143" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -41029,7 +41029,7 @@
         <x:v>hours</x:v>
       </x:c>
       <x:c r="K143" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L143" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -41041,7 +41041,7 @@
         <x:v>PLN-00865</x:v>
       </x:c>
       <x:c r="B144" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C144" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -41066,7 +41066,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K144" s="28" t="str">
-        <x:v>Approved labor-cost assumptions</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L144" s="34" t="str">
         <x:v>2026-06-30</x:v>
@@ -41078,7 +41078,7 @@
         <x:v>PLN-00866</x:v>
       </x:c>
       <x:c r="B145" s="28" t="str">
-        <x:v>Complete the backlog burn and capacity model</x:v>
+        <x:v>FY27 backlog delivery plan</x:v>
       </x:c>
       <x:c r="C145" s="28" t="str">
         <x:v>Capacity remediation</x:v>
@@ -41103,7 +41103,7 @@
         <x:v>USD per hour</x:v>
       </x:c>
       <x:c r="K145" s="28" t="str">
-        <x:v>Executed contingent labor framework</x:v>
+        <x:v>FY27 planning assumptions - v6 controller tie.xlsx</x:v>
       </x:c>
       <x:c r="L145" s="34" t="str">
         <x:v>2026-06-30</x:v>
